--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Digest.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Digest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -400,7 +400,15 @@
     <t>Very often, a server will also know of a resource that references the binary, and can automatically apply the appropriate access rules based on that reference. However, there are some circumstances where this is not appropriate, e.g. the binary is uploaded directly to the server without any linking resource, the binary is referred to from multiple different resources, and/or the binary is content such as an application logo that has less protection than any of the resources that reference it.</t>
   </si>
   <si>
-    <t>n/a</t>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Binary.data</t>
@@ -763,7 +771,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1601,21 +1609,21 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1638,16 +1646,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1697,7 +1705,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1712,7 +1720,7 @@
         <v>96</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Digest.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Digest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
